--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -399,27 +399,817 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:I4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>team</v>
+      </c>
+      <c r="C1" t="str">
+        <v>event</v>
+      </c>
+      <c r="D1" t="str">
+        <v>tier</v>
+      </c>
+      <c r="E1" t="str">
+        <v>scope</v>
+      </c>
+      <c r="F1" t="str">
+        <v>position</v>
+      </c>
+      <c r="G1" t="str">
+        <v>prizePool</v>
+      </c>
+      <c r="H1" t="str">
+        <v>wonAmount</v>
+      </c>
+      <c r="I1" t="str">
+        <v>month</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1783531248336</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="C2" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="G2">
+        <v>1790000</v>
+      </c>
+      <c r="H2">
+        <v>100000</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1783531237020</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="C3" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="G3">
+        <v>1790000</v>
+      </c>
+      <c r="H3">
+        <v>170000</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1783531219494</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="C4" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="G4">
+        <v>1790000</v>
+      </c>
+      <c r="H4">
+        <v>500000</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:J21"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>refId</v>
+      </c>
+      <c r="C1" t="str">
+        <v>player</v>
+      </c>
+      <c r="D1" t="str">
+        <v>team</v>
+      </c>
+      <c r="E1" t="str">
+        <v>kind</v>
+      </c>
+      <c r="F1" t="str">
+        <v>event</v>
+      </c>
+      <c r="G1" t="str">
+        <v>tier</v>
+      </c>
+      <c r="H1" t="str">
+        <v>scope</v>
+      </c>
+      <c r="I1" t="str">
+        <v>position</v>
+      </c>
+      <c r="J1" t="str">
+        <v>month</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1783531290361</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E2" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F2" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Third</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1783531284605</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E3" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F3" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1783531278450</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E4" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F4" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1783531271104</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E5" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F5" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1783531262507</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E6" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F6" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1783531248336-kyousuke</v>
+      </c>
+      <c r="B7">
+        <v>1783531248336</v>
+      </c>
+      <c r="C7" t="str">
+        <v>kyousuke</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E7" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F7" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1783531248336-kyxsan</v>
+      </c>
+      <c r="B8">
+        <v>1783531248336</v>
+      </c>
+      <c r="C8" t="str">
+        <v>kyxsan</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E8" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F8" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1783531248336-NiKo</v>
+      </c>
+      <c r="B9">
+        <v>1783531248336</v>
+      </c>
+      <c r="C9" t="str">
+        <v>NiKo</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E9" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F9" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1783531248336-TeSeS</v>
+      </c>
+      <c r="B10">
+        <v>1783531248336</v>
+      </c>
+      <c r="C10" t="str">
+        <v>TeSeS</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E10" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F10" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1783531248336-m0NESY</v>
+      </c>
+      <c r="B11">
+        <v>1783531248336</v>
+      </c>
+      <c r="C11" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E11" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F11" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1783531237020-mezii</v>
+      </c>
+      <c r="B12">
+        <v>1783531237020</v>
+      </c>
+      <c r="C12" t="str">
+        <v>mezii</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E12" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F12" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1783531237020-flameZ</v>
+      </c>
+      <c r="B13">
+        <v>1783531237020</v>
+      </c>
+      <c r="C13" t="str">
+        <v>flameZ</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E13" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F13" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>1783531237020-ropz</v>
+      </c>
+      <c r="B14">
+        <v>1783531237020</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E14" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F14" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>1783531237020-apEX</v>
+      </c>
+      <c r="B15">
+        <v>1783531237020</v>
+      </c>
+      <c r="C15" t="str">
+        <v>apEX</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E15" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F15" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>1783531237020-ZywOo</v>
+      </c>
+      <c r="B16">
+        <v>1783531237020</v>
+      </c>
+      <c r="C16" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E16" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F16" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1783531219494-history</v>
+      </c>
+      <c r="B17">
+        <v>1783531219494</v>
+      </c>
+      <c r="C17" t="str">
+        <v>history</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E17" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F17" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>1783531219494-heroghoxxt</v>
+      </c>
+      <c r="B18">
+        <v>1783531219494</v>
+      </c>
+      <c r="C18" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E18" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F18" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>1783531219494-SpavaQu</v>
+      </c>
+      <c r="B19">
+        <v>1783531219494</v>
+      </c>
+      <c r="C19" t="str">
+        <v>SpavaQu</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E19" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F19" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>1783531219494-Pelle</v>
+      </c>
+      <c r="B20">
+        <v>1783531219494</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Pelle</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E20" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F20" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>1783531219494-kilzys</v>
+      </c>
+      <c r="B21">
+        <v>1783531219494</v>
+      </c>
+      <c r="C21" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E21" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F21" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,7 +1239,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1783473413103</v>
+        <v>1783532394458</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -458,13 +1248,13 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D2" t="str">
-        <v>taco</v>
+        <v>diskyb0b</v>
       </c>
       <c r="E2" t="str">
         <v>Free Agency</v>
       </c>
       <c r="F2" t="str">
-        <v>Lux Tenebris</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -475,33 +1265,267 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>1783473388452</v>
+        <v>1783532378345</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D3" t="str">
-        <v>fer</v>
+        <v>Gizmy</v>
       </c>
       <c r="E3" t="str">
-        <v>Free Agency</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="F3" t="str">
-        <v>Lux Tenebris</v>
+        <v>Iluminar</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="str">
+        <v>CLAUSE DEAL · joined as Starter</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1783532335269</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D4" t="str">
+        <v>hades</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Mythic</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="str">
+        <v>joined as Starter</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1783532286477</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>TRANSFER</v>
+      </c>
+      <c r="D5" t="str">
+        <v>fl0m</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Mythic</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="str">
+        <v>CLAUSE DEAL · joined as Starter</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1783531772696</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D6" t="str">
+        <v>taco</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="str">
+        <v>joined as Starter</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1783531758984</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D7" t="str">
+        <v>fer</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <v>joined as Starter</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>1783531616692</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D8" t="str">
+        <v>kyourezz</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="str">
+        <v>joined as Starter</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1783531586211</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="str">
+        <v>TRANSFER</v>
+      </c>
+      <c r="D9" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G9">
+        <v>40000</v>
+      </c>
+      <c r="H9" t="str">
+        <v>CLAUSE DEAL · joined as Starter</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>1783531583393</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>TRANSFER</v>
+      </c>
+      <c r="D10" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G10">
+        <v>50000</v>
+      </c>
+      <c r="H10" t="str">
+        <v>CLAUSE DEAL · joined as Starter</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>1783473413103</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D11" t="str">
+        <v>taco</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="str">
+        <v>joined as Starter</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1783473388452</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D12" t="str">
+        <v>fer</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="str">
         <v>joined as Starter</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -1,43 +1,262 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\ck-tools-main\file\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9FA3AF-173E-4DE9-963E-D4F5399610FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="-2565" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="TeamHistory" sheetId="1" r:id="rId1"/>
     <sheet name="PlayerHistory" sheetId="2" r:id="rId2"/>
     <sheet name="Transactions" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="76">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>team</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>tier</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>prizePool</t>
+  </si>
+  <si>
+    <t>wonAmount</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>Falcons</t>
+  </si>
+  <si>
+    <t>DreamHack Winter 2026</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>Winner</t>
+  </si>
+  <si>
+    <t>Vitality</t>
+  </si>
+  <si>
+    <t>Iluminar</t>
+  </si>
+  <si>
+    <t>refId</t>
+  </si>
+  <si>
+    <t>player</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>m0NESY</t>
+  </si>
+  <si>
+    <t>VP</t>
+  </si>
+  <si>
+    <t>Third</t>
+  </si>
+  <si>
+    <t>ropz</t>
+  </si>
+  <si>
+    <t>Second</t>
+  </si>
+  <si>
+    <t>ZywOo</t>
+  </si>
+  <si>
+    <t>EVP</t>
+  </si>
+  <si>
+    <t>heroghoxxt</t>
+  </si>
+  <si>
+    <t>kilzys</t>
+  </si>
+  <si>
+    <t>MVP</t>
+  </si>
+  <si>
+    <t>1783531248336-kyousuke</t>
+  </si>
+  <si>
+    <t>kyousuke</t>
+  </si>
+  <si>
+    <t>EVENT</t>
+  </si>
+  <si>
+    <t>1783531248336-kyxsan</t>
+  </si>
+  <si>
+    <t>kyxsan</t>
+  </si>
+  <si>
+    <t>1783531248336-NiKo</t>
+  </si>
+  <si>
+    <t>NiKo</t>
+  </si>
+  <si>
+    <t>1783531248336-TeSeS</t>
+  </si>
+  <si>
+    <t>TeSeS</t>
+  </si>
+  <si>
+    <t>1783531248336-m0NESY</t>
+  </si>
+  <si>
+    <t>1783531237020-mezii</t>
+  </si>
+  <si>
+    <t>mezii</t>
+  </si>
+  <si>
+    <t>1783531237020-flameZ</t>
+  </si>
+  <si>
+    <t>flameZ</t>
+  </si>
+  <si>
+    <t>1783531237020-ropz</t>
+  </si>
+  <si>
+    <t>1783531237020-apEX</t>
+  </si>
+  <si>
+    <t>apEX</t>
+  </si>
+  <si>
+    <t>1783531237020-ZywOo</t>
+  </si>
+  <si>
+    <t>1783531219494-history</t>
+  </si>
+  <si>
+    <t>history</t>
+  </si>
+  <si>
+    <t>1783531219494-heroghoxxt</t>
+  </si>
+  <si>
+    <t>1783531219494-SpavaQu</t>
+  </si>
+  <si>
+    <t>SpavaQu</t>
+  </si>
+  <si>
+    <t>1783531219494-Pelle</t>
+  </si>
+  <si>
+    <t>Pelle</t>
+  </si>
+  <si>
+    <t>1783531219494-kilzys</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>playerName</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>FA SIGNING</t>
+  </si>
+  <si>
+    <t>diskyb0b</t>
+  </si>
+  <si>
+    <t>Free Agency</t>
+  </si>
+  <si>
+    <t>Kappa Bar</t>
+  </si>
+  <si>
+    <t>joined as Starter</t>
+  </si>
+  <si>
+    <t>TRANSFER</t>
+  </si>
+  <si>
+    <t>Gizmy</t>
+  </si>
+  <si>
+    <t>CLAUSE DEAL · joined as Starter</t>
+  </si>
+  <si>
+    <t>hades</t>
+  </si>
+  <si>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>fl0m</t>
+  </si>
+  <si>
+    <t>taco</t>
+  </si>
+  <si>
+    <t>Lux Tenebris</t>
+  </si>
+  <si>
+    <t>fer</t>
+  </si>
+  <si>
+    <t>kyourezz</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -67,13 +286,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,56 +625,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>team</v>
-      </c>
-      <c r="C1" t="str">
-        <v>event</v>
-      </c>
-      <c r="D1" t="str">
-        <v>tier</v>
-      </c>
-      <c r="E1" t="str">
-        <v>scope</v>
-      </c>
-      <c r="F1" t="str">
-        <v>position</v>
-      </c>
-      <c r="G1" t="str">
-        <v>prizePool</v>
-      </c>
-      <c r="H1" t="str">
-        <v>wonAmount</v>
-      </c>
-      <c r="I1" t="str">
-        <v>month</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1783531248336</v>
       </c>
-      <c r="B2" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="C2" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
-      <c r="E2" t="str">
-        <v>Global</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Winner</v>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
       </c>
       <c r="G2">
         <v>1790000</v>
@@ -459,24 +687,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1783531237020</v>
       </c>
-      <c r="B3" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="C3" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
-      <c r="E3" t="str">
-        <v>Global</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Winner</v>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
       </c>
       <c r="G3">
         <v>1790000</v>
@@ -488,24 +716,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1783531219494</v>
       </c>
-      <c r="B4" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="C4" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
       </c>
       <c r="D4">
         <v>5</v>
       </c>
-      <c r="E4" t="str">
-        <v>Global</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Winner</v>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
       </c>
       <c r="G4">
         <v>1790000</v>
@@ -518,1014 +746,1019 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError sqref="A1:I1 A4:E4 A3:E3 G3:I3 G4:I4 A2:E2 G2:I2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>refId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>player</v>
-      </c>
-      <c r="D1" t="str">
-        <v>team</v>
-      </c>
-      <c r="E1" t="str">
-        <v>kind</v>
-      </c>
-      <c r="F1" t="str">
-        <v>event</v>
-      </c>
-      <c r="G1" t="str">
-        <v>tier</v>
-      </c>
-      <c r="H1" t="str">
-        <v>scope</v>
-      </c>
-      <c r="I1" t="str">
-        <v>position</v>
-      </c>
-      <c r="J1" t="str">
-        <v>month</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1783531290361</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v>m0NESY</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E2" t="str">
-        <v>VP</v>
-      </c>
-      <c r="F2" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
       </c>
       <c r="G2">
         <v>5</v>
       </c>
-      <c r="H2" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Third</v>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1783531284605</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v>ropz</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="E3" t="str">
-        <v>VP</v>
-      </c>
-      <c r="F3" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
-      <c r="H3" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Second</v>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1783531278450</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v>ZywOo</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="E4" t="str">
-        <v>EVP</v>
-      </c>
-      <c r="F4" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
-      <c r="H4" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Second</v>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1783531271104</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v>heroghoxxt</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="E5" t="str">
-        <v>VP</v>
-      </c>
-      <c r="F5" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
       </c>
       <c r="G5">
         <v>5</v>
       </c>
-      <c r="H5" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Winner</v>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1783531262507</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v>kilzys</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="E6" t="str">
-        <v>MVP</v>
-      </c>
-      <c r="F6" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
-      <c r="H6" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Winner</v>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>1783531248336-kyousuke</v>
+    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
       </c>
       <c r="B7">
         <v>1783531248336</v>
       </c>
-      <c r="C7" t="str">
-        <v>kyousuke</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E7" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F7" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
-      <c r="H7" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Winner</v>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1783531248336-kyxsan</v>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
       </c>
       <c r="B8">
         <v>1783531248336</v>
       </c>
-      <c r="C8" t="str">
-        <v>kyxsan</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E8" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F8" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
-      <c r="H8" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Winner</v>
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1783531248336-NiKo</v>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>34</v>
       </c>
       <c r="B9">
         <v>1783531248336</v>
       </c>
-      <c r="C9" t="str">
-        <v>NiKo</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E9" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F9" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
-      <c r="H9" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Winner</v>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" t="s">
+        <v>21</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1783531248336-TeSeS</v>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>36</v>
       </c>
       <c r="B10">
         <v>1783531248336</v>
       </c>
-      <c r="C10" t="str">
-        <v>TeSeS</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E10" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F10" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Winner</v>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" t="s">
+        <v>21</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1783531248336-m0NESY</v>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>38</v>
       </c>
       <c r="B11">
         <v>1783531248336</v>
       </c>
-      <c r="C11" t="str">
-        <v>m0NESY</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E11" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F11" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
-      <c r="H11" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Winner</v>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" t="s">
+        <v>21</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1783531237020-mezii</v>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>39</v>
       </c>
       <c r="B12">
         <v>1783531237020</v>
       </c>
-      <c r="C12" t="str">
-        <v>mezii</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="E12" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F12" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I12" t="str">
-        <v>Winner</v>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1783531237020-flameZ</v>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>41</v>
       </c>
       <c r="B13">
         <v>1783531237020</v>
       </c>
-      <c r="C13" t="str">
-        <v>flameZ</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="E13" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F13" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
-      <c r="H13" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Winner</v>
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>1783531237020-ropz</v>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>43</v>
       </c>
       <c r="B14">
         <v>1783531237020</v>
       </c>
-      <c r="C14" t="str">
-        <v>ropz</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="E14" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F14" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
-      <c r="H14" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Winner</v>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>1783531237020-apEX</v>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>44</v>
       </c>
       <c r="B15">
         <v>1783531237020</v>
       </c>
-      <c r="C15" t="str">
-        <v>apEX</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="E15" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F15" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
-      <c r="H15" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I15" t="str">
-        <v>Winner</v>
+      <c r="H15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>1783531237020-ZywOo</v>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>46</v>
       </c>
       <c r="B16">
         <v>1783531237020</v>
       </c>
-      <c r="C16" t="str">
-        <v>ZywOo</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="E16" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F16" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
-      <c r="H16" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I16" t="str">
-        <v>Winner</v>
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1783531219494-history</v>
+    <row r="17" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>47</v>
       </c>
       <c r="B17">
         <v>1783531219494</v>
       </c>
-      <c r="C17" t="str">
-        <v>history</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="E17" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F17" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
-      <c r="H17" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Winner</v>
+      <c r="H17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" t="s">
+        <v>12</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>1783531219494-heroghoxxt</v>
+    <row r="18" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>49</v>
       </c>
       <c r="B18">
         <v>1783531219494</v>
       </c>
-      <c r="C18" t="str">
-        <v>heroghoxxt</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="E18" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F18" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
-      <c r="H18" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I18" t="str">
-        <v>Winner</v>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" t="s">
+        <v>12</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>1783531219494-SpavaQu</v>
+    <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>50</v>
       </c>
       <c r="B19">
         <v>1783531219494</v>
       </c>
-      <c r="C19" t="str">
-        <v>SpavaQu</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="E19" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F19" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
-      <c r="H19" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I19" t="str">
-        <v>Winner</v>
+      <c r="H19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" t="s">
+        <v>12</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>1783531219494-Pelle</v>
+    <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>52</v>
       </c>
       <c r="B20">
         <v>1783531219494</v>
       </c>
-      <c r="C20" t="str">
-        <v>Pelle</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="E20" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F20" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
-      <c r="H20" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I20" t="str">
-        <v>Winner</v>
+      <c r="H20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" t="s">
+        <v>12</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>1783531219494-kilzys</v>
+    <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>54</v>
       </c>
       <c r="B21">
         <v>1783531219494</v>
       </c>
-      <c r="C21" t="str">
-        <v>kilzys</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="E21" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F21" t="str">
-        <v>DreamHack Winter 2026</v>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
-      <c r="H21" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I21" t="str">
-        <v>Winner</v>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" t="s">
+        <v>12</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J21"/>
+    <ignoredError sqref="A1:J6 A17:J21 A7:H7 J7 A8:H8 J8 A9:H9 J9 A10:H10 J10 A11:H11 J11 A12:H12 J12 A13:H13 J13 A14:H14 J14 A15:H15 J15 A16:H16 J16" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>month</v>
-      </c>
-      <c r="C1" t="str">
-        <v>type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>playerName</v>
-      </c>
-      <c r="E1" t="str">
-        <v>from</v>
-      </c>
-      <c r="F1" t="str">
-        <v>to</v>
-      </c>
-      <c r="G1" t="str">
-        <v>amount</v>
-      </c>
-      <c r="H1" t="str">
-        <v>note</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1783532394458</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="str">
-        <v>FA SIGNING</v>
-      </c>
-      <c r="D2" t="str">
-        <v>diskyb0b</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Free Agency</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Kappa Bar</v>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" t="s">
+        <v>64</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" t="str">
-        <v>joined as Starter</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="H2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1783532378345</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="str">
-        <v>TRANSFER</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Gizmy</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Kappa Bar</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Iluminar</v>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="H3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1783532335269</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="str">
-        <v>FA SIGNING</v>
-      </c>
-      <c r="D4" t="str">
-        <v>hades</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Free Agency</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Mythic</v>
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" t="s">
+        <v>70</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" t="str">
-        <v>joined as Starter</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="H4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1783532286477</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="str">
-        <v>TRANSFER</v>
-      </c>
-      <c r="D5" t="str">
-        <v>fl0m</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Mythic</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Iluminar</v>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="H5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1783531772696</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="str">
-        <v>FA SIGNING</v>
-      </c>
-      <c r="D6" t="str">
-        <v>taco</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Free Agency</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Lux Tenebris</v>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
+        <v>73</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" t="str">
-        <v>joined as Starter</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="H6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1783531758984</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="str">
-        <v>FA SIGNING</v>
-      </c>
-      <c r="D7" t="str">
-        <v>fer</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Free Agency</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Lux Tenebris</v>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" t="s">
+        <v>73</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" t="str">
-        <v>joined as Starter</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="H7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1783531616692</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="str">
-        <v>FA SIGNING</v>
-      </c>
-      <c r="D8" t="str">
-        <v>kyourezz</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Free Agency</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Lux Tenebris</v>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" t="s">
+        <v>73</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" t="str">
-        <v>joined as Starter</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="H8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1783531586211</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="str">
-        <v>TRANSFER</v>
-      </c>
-      <c r="D9" t="str">
-        <v>heroghoxxt</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Lux Tenebris</v>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>73</v>
       </c>
       <c r="G9">
         <v>40000</v>
       </c>
-      <c r="H9" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="H9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1783531583393</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" t="str">
-        <v>TRANSFER</v>
-      </c>
-      <c r="D10" t="str">
-        <v>kilzys</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Lux Tenebris</v>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>73</v>
       </c>
       <c r="G10">
         <v>50000</v>
       </c>
-      <c r="H10" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="H10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1783473413103</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="str">
-        <v>FA SIGNING</v>
-      </c>
-      <c r="D11" t="str">
-        <v>taco</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Free Agency</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Lux Tenebris</v>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>73</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
-      <c r="H11" t="str">
-        <v>joined as Starter</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1783473388452</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="str">
-        <v>FA SIGNING</v>
-      </c>
-      <c r="D12" t="str">
-        <v>fer</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Free Agency</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Lux Tenebris</v>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="H12" t="str">
-        <v>joined as Starter</v>
+      <c r="H12" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+    <ignoredError sqref="A1:H12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,28 +434,28 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1784848026994</v>
+        <v>1784854079769</v>
       </c>
       <c r="B2" t="str">
-        <v>FURIA</v>
+        <v>Entropiq</v>
       </c>
       <c r="C2" t="str">
-        <v>Tournament Payout</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F2" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="G2">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="H2">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -463,28 +463,28 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>1783531248336</v>
+        <v>1784854026526</v>
       </c>
       <c r="B3" t="str">
-        <v>Falcons</v>
+        <v>AMKAL</v>
       </c>
       <c r="C3" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F3" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="G3">
-        <v>1790000</v>
+        <v>2000</v>
       </c>
       <c r="H3">
-        <v>100000</v>
+        <v>1200</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -492,28 +492,28 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1783531237020</v>
+        <v>1784848026994</v>
       </c>
       <c r="B4" t="str">
-        <v>Vitality</v>
+        <v>FURIA</v>
       </c>
       <c r="C4" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F4" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="G4">
-        <v>1790000</v>
+        <v>3000</v>
       </c>
       <c r="H4">
-        <v>170000</v>
+        <v>1800</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -521,10 +521,10 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1783531219494</v>
+        <v>1783531248336</v>
       </c>
       <c r="B5" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="C5" t="str">
         <v>DreamHack Winter 2026</v>
@@ -536,28 +536,86 @@
         <v>Global</v>
       </c>
       <c r="F5" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="G5">
         <v>1790000</v>
       </c>
       <c r="H5">
+        <v>100000</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1783531237020</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="C6" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Second</v>
+      </c>
+      <c r="G6">
+        <v>1790000</v>
+      </c>
+      <c r="H6">
+        <v>170000</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1783531219494</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="C7" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="G7">
+        <v>1790000</v>
+      </c>
+      <c r="H7">
         <v>500000</v>
       </c>
-      <c r="I5">
+      <c r="I7">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -593,31 +651,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1784848026994-molodoy</v>
+        <v>1784854079769-Benkai</v>
       </c>
       <c r="B2">
-        <v>1784848026994</v>
+        <v>1784854079769</v>
       </c>
       <c r="C2" t="str">
-        <v>molodoy</v>
+        <v>Benkai</v>
       </c>
       <c r="D2" t="str">
-        <v>FURIA</v>
+        <v>Entropiq</v>
       </c>
       <c r="E2" t="str">
         <v>EVENT</v>
       </c>
       <c r="F2" t="str">
-        <v>Tournament Payout</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I2" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -625,31 +683,31 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>1784848026994-KSCERATO</v>
+        <v>1784854079769-dea</v>
       </c>
       <c r="B3">
-        <v>1784848026994</v>
+        <v>1784854079769</v>
       </c>
       <c r="C3" t="str">
-        <v>KSCERATO</v>
+        <v>dea</v>
       </c>
       <c r="D3" t="str">
-        <v>FURIA</v>
+        <v>Entropiq</v>
       </c>
       <c r="E3" t="str">
         <v>EVENT</v>
       </c>
       <c r="F3" t="str">
-        <v>Tournament Payout</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I3" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -657,31 +715,31 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1784848026994-YEKINDAR</v>
+        <v>1784854079769-shane</v>
       </c>
       <c r="B4">
-        <v>1784848026994</v>
+        <v>1784854079769</v>
       </c>
       <c r="C4" t="str">
-        <v>YEKINDAR</v>
+        <v>shane</v>
       </c>
       <c r="D4" t="str">
-        <v>FURIA</v>
+        <v>Entropiq</v>
       </c>
       <c r="E4" t="str">
         <v>EVENT</v>
       </c>
       <c r="F4" t="str">
-        <v>Tournament Payout</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I4" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -689,31 +747,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1784848026994-yuurih</v>
+        <v>1784854079769-nosraC</v>
       </c>
       <c r="B5">
-        <v>1784848026994</v>
+        <v>1784854079769</v>
       </c>
       <c r="C5" t="str">
-        <v>yuurih</v>
+        <v>nosraC</v>
       </c>
       <c r="D5" t="str">
-        <v>FURIA</v>
+        <v>Entropiq</v>
       </c>
       <c r="E5" t="str">
         <v>EVENT</v>
       </c>
       <c r="F5" t="str">
-        <v>Tournament Payout</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I5" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -721,316 +779,316 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1784848026994-FalleN</v>
+        <v>1784854079769-MarKE</v>
       </c>
       <c r="B6">
-        <v>1784848026994</v>
+        <v>1784854079769</v>
       </c>
       <c r="C6" t="str">
-        <v>FalleN</v>
+        <v>MarKE</v>
       </c>
       <c r="D6" t="str">
-        <v>FURIA</v>
+        <v>Entropiq</v>
       </c>
       <c r="E6" t="str">
         <v>EVENT</v>
       </c>
       <c r="F6" t="str">
-        <v>Tournament Payout</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I6" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>1784847962039</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="A7" t="str">
+        <v>1784854026526-ivz</v>
+      </c>
+      <c r="B7">
+        <v>1784854026526</v>
       </c>
       <c r="C7" t="str">
-        <v>abizz</v>
+        <v>ivz</v>
       </c>
       <c r="D7" t="str">
         <v>AMKAL</v>
       </c>
       <c r="E7" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F7" t="str">
-        <v>Operations Grant</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="H7" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I7" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>1784847955956</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="A8" t="str">
+        <v>1784854026526-abizz</v>
+      </c>
+      <c r="B8">
+        <v>1784854026526</v>
       </c>
       <c r="C8" t="str">
-        <v>next</v>
+        <v>abizz</v>
       </c>
       <c r="D8" t="str">
         <v>AMKAL</v>
       </c>
       <c r="E8" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F8" t="str">
-        <v>Operations Grant</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I8" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1784854026526-nacho</v>
+      </c>
+      <c r="B9">
+        <v>1784854026526</v>
+      </c>
+      <c r="C9" t="str">
+        <v>nacho</v>
+      </c>
+      <c r="D9" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E9" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F9" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1784854026526-BK1</v>
+      </c>
+      <c r="B10">
+        <v>1784854026526</v>
+      </c>
+      <c r="C10" t="str">
+        <v>BK1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E10" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F10" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1784854026526-next</v>
+      </c>
+      <c r="B11">
+        <v>1784854026526</v>
+      </c>
+      <c r="C11" t="str">
+        <v>next</v>
+      </c>
+      <c r="D11" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E11" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F11" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1784848026994-molodoy</v>
+      </c>
+      <c r="B12">
+        <v>1784848026994</v>
+      </c>
+      <c r="C12" t="str">
+        <v>molodoy</v>
+      </c>
+      <c r="D12" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E12" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F12" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I12" t="str">
         <v>Winner</v>
       </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>1784847948890</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
+      <c r="J12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1784848026994-KSCERATO</v>
+      </c>
+      <c r="B13">
+        <v>1784848026994</v>
+      </c>
+      <c r="C13" t="str">
+        <v>KSCERATO</v>
+      </c>
+      <c r="D13" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E13" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F13" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>1784848026994-YEKINDAR</v>
+      </c>
+      <c r="B14">
+        <v>1784848026994</v>
+      </c>
+      <c r="C14" t="str">
+        <v>YEKINDAR</v>
+      </c>
+      <c r="D14" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E14" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F14" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>1784848026994-yuurih</v>
+      </c>
+      <c r="B15">
+        <v>1784848026994</v>
+      </c>
+      <c r="C15" t="str">
         <v>yuurih</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D15" t="str">
         <v>FURIA</v>
       </c>
-      <c r="E9" t="str">
-        <v>VP</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Operations Grant</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Winner</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>1784847943609</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v>KSCERATO</v>
-      </c>
-      <c r="D10" t="str">
-        <v>FURIA</v>
-      </c>
-      <c r="E10" t="str">
-        <v>EVP</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Operations Grant</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Winner</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>1784847935905</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v>molodoy</v>
-      </c>
-      <c r="D11" t="str">
-        <v>FURIA</v>
-      </c>
-      <c r="E11" t="str">
-        <v>MVP</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Operations Grant</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Winner</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>1783531290361</v>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v>m0NESY</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E12" t="str">
-        <v>VP</v>
-      </c>
-      <c r="F12" t="str">
-        <v>DreamHack Winter 2026</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I12" t="str">
-        <v>Third</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>1783531284605</v>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v>ropz</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="E13" t="str">
-        <v>VP</v>
-      </c>
-      <c r="F13" t="str">
-        <v>DreamHack Winter 2026</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Second</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>1783531278450</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v>ZywOo</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="E14" t="str">
-        <v>EVP</v>
-      </c>
-      <c r="F14" t="str">
-        <v>DreamHack Winter 2026</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Second</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>1783531271104</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v>heroghoxxt</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Iluminar</v>
-      </c>
       <c r="E15" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F15" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I15" t="str">
         <v>Winner</v>
@@ -1040,29 +1098,29 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>1783531262507</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
+      <c r="A16" t="str">
+        <v>1784848026994-FalleN</v>
+      </c>
+      <c r="B16">
+        <v>1784848026994</v>
       </c>
       <c r="C16" t="str">
-        <v>kilzys</v>
+        <v>FalleN</v>
       </c>
       <c r="D16" t="str">
-        <v>Iluminar</v>
+        <v>FURIA</v>
       </c>
       <c r="E16" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F16" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I16" t="str">
         <v>Winner</v>
@@ -1072,180 +1130,180 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>1783531248336-kyousuke</v>
-      </c>
-      <c r="B17">
-        <v>1783531248336</v>
+      <c r="A17">
+        <v>1784847962039</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
       </c>
       <c r="C17" t="str">
-        <v>kyousuke</v>
+        <v>abizz</v>
       </c>
       <c r="D17" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E17" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F17" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>1784847955956</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v>next</v>
+      </c>
+      <c r="D18" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E18" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F18" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>1784847948890</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>yuurih</v>
+      </c>
+      <c r="D19" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E19" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F19" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>1784847943609</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>KSCERATO</v>
+      </c>
+      <c r="D20" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E20" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F20" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>1784847935905</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>molodoy</v>
+      </c>
+      <c r="D21" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E21" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F21" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>1783531290361</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D22" t="str">
         <v>Falcons</v>
       </c>
-      <c r="E17" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F17" t="str">
-        <v>DreamHack Winter 2026</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Third</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>1783531248336-kyxsan</v>
-      </c>
-      <c r="B18">
-        <v>1783531248336</v>
-      </c>
-      <c r="C18" t="str">
-        <v>kyxsan</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E18" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F18" t="str">
-        <v>DreamHack Winter 2026</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I18" t="str">
-        <v>Third</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>1783531248336-NiKo</v>
-      </c>
-      <c r="B19">
-        <v>1783531248336</v>
-      </c>
-      <c r="C19" t="str">
-        <v>NiKo</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E19" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F19" t="str">
-        <v>DreamHack Winter 2026</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I19" t="str">
-        <v>Third</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>1783531248336-TeSeS</v>
-      </c>
-      <c r="B20">
-        <v>1783531248336</v>
-      </c>
-      <c r="C20" t="str">
-        <v>TeSeS</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E20" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F20" t="str">
-        <v>DreamHack Winter 2026</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I20" t="str">
-        <v>Third</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>1783531248336-m0NESY</v>
-      </c>
-      <c r="B21">
-        <v>1783531248336</v>
-      </c>
-      <c r="C21" t="str">
-        <v>m0NESY</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="E21" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F21" t="str">
-        <v>DreamHack Winter 2026</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I21" t="str">
-        <v>Third</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>1783531237020-mezii</v>
-      </c>
-      <c r="B22">
-        <v>1783531237020</v>
-      </c>
-      <c r="C22" t="str">
-        <v>mezii</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Vitality</v>
-      </c>
       <c r="E22" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F22" t="str">
         <v>DreamHack Winter 2026</v>
@@ -1257,27 +1315,27 @@
         <v>Global</v>
       </c>
       <c r="I22" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="J22">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>1783531237020-flameZ</v>
-      </c>
-      <c r="B23">
-        <v>1783531237020</v>
+      <c r="A23">
+        <v>1783531284605</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
       </c>
       <c r="C23" t="str">
-        <v>flameZ</v>
+        <v>ropz</v>
       </c>
       <c r="D23" t="str">
         <v>Vitality</v>
       </c>
       <c r="E23" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F23" t="str">
         <v>DreamHack Winter 2026</v>
@@ -1296,20 +1354,20 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>1783531237020-ropz</v>
-      </c>
-      <c r="B24">
-        <v>1783531237020</v>
+      <c r="A24">
+        <v>1783531278450</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
       </c>
       <c r="C24" t="str">
-        <v>ropz</v>
+        <v>ZywOo</v>
       </c>
       <c r="D24" t="str">
         <v>Vitality</v>
       </c>
       <c r="E24" t="str">
-        <v>EVENT</v>
+        <v>EVP</v>
       </c>
       <c r="F24" t="str">
         <v>DreamHack Winter 2026</v>
@@ -1328,20 +1386,20 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>1783531237020-apEX</v>
-      </c>
-      <c r="B25">
-        <v>1783531237020</v>
+      <c r="A25">
+        <v>1783531271104</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
       </c>
       <c r="C25" t="str">
-        <v>apEX</v>
+        <v>heroghoxxt</v>
       </c>
       <c r="D25" t="str">
-        <v>Vitality</v>
+        <v>Iluminar</v>
       </c>
       <c r="E25" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F25" t="str">
         <v>DreamHack Winter 2026</v>
@@ -1353,27 +1411,27 @@
         <v>Global</v>
       </c>
       <c r="I25" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>1783531237020-ZywOo</v>
-      </c>
-      <c r="B26">
-        <v>1783531237020</v>
+      <c r="A26">
+        <v>1783531262507</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
       </c>
       <c r="C26" t="str">
-        <v>ZywOo</v>
+        <v>kilzys</v>
       </c>
       <c r="D26" t="str">
-        <v>Vitality</v>
+        <v>Iluminar</v>
       </c>
       <c r="E26" t="str">
-        <v>EVENT</v>
+        <v>MVP</v>
       </c>
       <c r="F26" t="str">
         <v>DreamHack Winter 2026</v>
@@ -1385,7 +1443,7 @@
         <v>Global</v>
       </c>
       <c r="I26" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1393,16 +1451,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>1783531219494-history</v>
+        <v>1783531248336-kyousuke</v>
       </c>
       <c r="B27">
-        <v>1783531219494</v>
+        <v>1783531248336</v>
       </c>
       <c r="C27" t="str">
-        <v>history</v>
+        <v>kyousuke</v>
       </c>
       <c r="D27" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="E27" t="str">
         <v>EVENT</v>
@@ -1417,7 +1475,7 @@
         <v>Global</v>
       </c>
       <c r="I27" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1425,16 +1483,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>1783531219494-heroghoxxt</v>
+        <v>1783531248336-kyxsan</v>
       </c>
       <c r="B28">
-        <v>1783531219494</v>
+        <v>1783531248336</v>
       </c>
       <c r="C28" t="str">
-        <v>heroghoxxt</v>
+        <v>kyxsan</v>
       </c>
       <c r="D28" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="E28" t="str">
         <v>EVENT</v>
@@ -1449,7 +1507,7 @@
         <v>Global</v>
       </c>
       <c r="I28" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1457,16 +1515,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>1783531219494-SpavaQu</v>
+        <v>1783531248336-NiKo</v>
       </c>
       <c r="B29">
-        <v>1783531219494</v>
+        <v>1783531248336</v>
       </c>
       <c r="C29" t="str">
-        <v>SpavaQu</v>
+        <v>NiKo</v>
       </c>
       <c r="D29" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="E29" t="str">
         <v>EVENT</v>
@@ -1481,7 +1539,7 @@
         <v>Global</v>
       </c>
       <c r="I29" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1489,16 +1547,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>1783531219494-Pelle</v>
+        <v>1783531248336-TeSeS</v>
       </c>
       <c r="B30">
-        <v>1783531219494</v>
+        <v>1783531248336</v>
       </c>
       <c r="C30" t="str">
-        <v>Pelle</v>
+        <v>TeSeS</v>
       </c>
       <c r="D30" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="E30" t="str">
         <v>EVENT</v>
@@ -1513,7 +1571,7 @@
         <v>Global</v>
       </c>
       <c r="I30" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1521,16 +1579,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>1783531219494-kilzys</v>
+        <v>1783531248336-m0NESY</v>
       </c>
       <c r="B31">
-        <v>1783531219494</v>
+        <v>1783531248336</v>
       </c>
       <c r="C31" t="str">
-        <v>kilzys</v>
+        <v>m0NESY</v>
       </c>
       <c r="D31" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="E31" t="str">
         <v>EVENT</v>
@@ -1545,15 +1603,335 @@
         <v>Global</v>
       </c>
       <c r="I31" t="str">
+        <v>Third</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>1783531237020-mezii</v>
+      </c>
+      <c r="B32">
+        <v>1783531237020</v>
+      </c>
+      <c r="C32" t="str">
+        <v>mezii</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E32" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F32" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>1783531237020-flameZ</v>
+      </c>
+      <c r="B33">
+        <v>1783531237020</v>
+      </c>
+      <c r="C33" t="str">
+        <v>flameZ</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E33" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F33" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>1783531237020-ropz</v>
+      </c>
+      <c r="B34">
+        <v>1783531237020</v>
+      </c>
+      <c r="C34" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E34" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F34" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>1783531237020-apEX</v>
+      </c>
+      <c r="B35">
+        <v>1783531237020</v>
+      </c>
+      <c r="C35" t="str">
+        <v>apEX</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E35" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F35" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>1783531237020-ZywOo</v>
+      </c>
+      <c r="B36">
+        <v>1783531237020</v>
+      </c>
+      <c r="C36" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E36" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F36" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>1783531219494-history</v>
+      </c>
+      <c r="B37">
+        <v>1783531219494</v>
+      </c>
+      <c r="C37" t="str">
+        <v>history</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E37" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F37" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I37" t="str">
         <v>Winner</v>
       </c>
-      <c r="J31">
+      <c r="J37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>1783531219494-heroghoxxt</v>
+      </c>
+      <c r="B38">
+        <v>1783531219494</v>
+      </c>
+      <c r="C38" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E38" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F38" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>1783531219494-SpavaQu</v>
+      </c>
+      <c r="B39">
+        <v>1783531219494</v>
+      </c>
+      <c r="C39" t="str">
+        <v>SpavaQu</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E39" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F39" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>1783531219494-Pelle</v>
+      </c>
+      <c r="B40">
+        <v>1783531219494</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Pelle</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E40" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F40" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>1783531219494-kilzys</v>
+      </c>
+      <c r="B41">
+        <v>1783531219494</v>
+      </c>
+      <c r="C41" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E41" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F41" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G41">
+        <v>5</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J41">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J41"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -1938,7 +1938,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1968,59 +1968,59 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1783532394458</v>
+        <v>1785396043745</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>FA SIGNING</v>
+        <v>PROMOTED</v>
       </c>
       <c r="D2" t="str">
-        <v>diskyb0b</v>
+        <v>boltz</v>
       </c>
       <c r="E2" t="str">
-        <v>Free Agency</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="F2" t="str">
-        <v>Kappa Bar</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="str">
-        <v>joined as Starter</v>
+        <v>promoted to starter</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1783532378345</v>
+        <v>1785396042996</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>TRANSFER</v>
+        <v>BENCHED</v>
       </c>
       <c r="D3" t="str">
-        <v>Gizmy</v>
+        <v>fer</v>
       </c>
       <c r="E3" t="str">
-        <v>Kappa Bar</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="F3" t="str">
-        <v>Iluminar</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>moved to bench</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1783532335269</v>
+        <v>1785396011356</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2029,76 +2029,76 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D4" t="str">
-        <v>hades</v>
+        <v>boltz</v>
       </c>
       <c r="E4" t="str">
         <v>Free Agency</v>
       </c>
       <c r="F4" t="str">
-        <v>Mythic</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="str">
-        <v>joined as Starter</v>
+        <v>joined as Bench</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>1783532286477</v>
+        <v>1783532394458</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D5" t="str">
-        <v>fl0m</v>
+        <v>diskyb0b</v>
       </c>
       <c r="E5" t="str">
-        <v>Mythic</v>
+        <v>Free Agency</v>
       </c>
       <c r="F5" t="str">
-        <v>Iluminar</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Starter</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1783531772696</v>
+        <v>1783532378345</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D6" t="str">
-        <v>taco</v>
+        <v>Gizmy</v>
       </c>
       <c r="E6" t="str">
-        <v>Free Agency</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="F6" t="str">
-        <v>Lux Tenebris</v>
+        <v>Iluminar</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="str">
-        <v>joined as Starter</v>
+        <v>CLAUSE DEAL · joined as Starter</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>1783531758984</v>
+        <v>1783532335269</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2107,13 +2107,13 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D7" t="str">
-        <v>fer</v>
+        <v>hades</v>
       </c>
       <c r="E7" t="str">
         <v>Free Agency</v>
       </c>
       <c r="F7" t="str">
-        <v>Lux Tenebris</v>
+        <v>Mythic</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2124,85 +2124,85 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>1783531616692</v>
+        <v>1783532286477</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D8" t="str">
-        <v>kyourezz</v>
+        <v>fl0m</v>
       </c>
       <c r="E8" t="str">
-        <v>Free Agency</v>
+        <v>Mythic</v>
       </c>
       <c r="F8" t="str">
-        <v>Lux Tenebris</v>
+        <v>Iluminar</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="str">
-        <v>joined as Starter</v>
+        <v>CLAUSE DEAL · joined as Starter</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>1783531586211</v>
+        <v>1783531772696</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D9" t="str">
-        <v>heroghoxxt</v>
+        <v>taco</v>
       </c>
       <c r="E9" t="str">
-        <v>Iluminar</v>
+        <v>Free Agency</v>
       </c>
       <c r="F9" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="G9">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="H9" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Starter</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>1783531583393</v>
+        <v>1783531758984</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D10" t="str">
-        <v>kilzys</v>
+        <v>fer</v>
       </c>
       <c r="E10" t="str">
-        <v>Iluminar</v>
+        <v>Free Agency</v>
       </c>
       <c r="F10" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="G10">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="H10" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Starter</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>1783473413103</v>
+        <v>1783531616692</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2211,7 +2211,7 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D11" t="str">
-        <v>taco</v>
+        <v>kyourezz</v>
       </c>
       <c r="E11" t="str">
         <v>Free Agency</v>
@@ -2228,43 +2228,168 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>1783473388452</v>
+        <v>1783531586211</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D12" t="str">
-        <v>fer</v>
+        <v>heroghoxxt</v>
       </c>
       <c r="E12" t="str">
-        <v>Free Agency</v>
+        <v>Iluminar</v>
       </c>
       <c r="F12" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="G12">
+        <v>40000</v>
+      </c>
+      <c r="H12" t="str">
+        <v>CLAUSE DEAL · joined as Starter</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>1783531583393</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="str">
+        <v>TRANSFER</v>
+      </c>
+      <c r="D13" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G13">
+        <v>50000</v>
+      </c>
+      <c r="H13" t="str">
+        <v>CLAUSE DEAL · joined as Starter</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>1783473413103</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D14" t="str">
+        <v>taco</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G14">
         <v>0</v>
       </c>
-      <c r="H12" t="str">
+      <c r="H14" t="str">
+        <v>joined as Starter</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>1783473388452</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D15" t="str">
+        <v>fer</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="str">
         <v>joined as Starter</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:G2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>playerName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>buyer</v>
+      </c>
+      <c r="D1" t="str">
+        <v>seller</v>
+      </c>
+      <c r="E1" t="str">
+        <v>amount</v>
+      </c>
+      <c r="F1" t="str">
+        <v>status</v>
+      </c>
+      <c r="G1" t="str">
+        <v>month</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1785396010605</v>
+      </c>
+      <c r="B2" t="str">
+        <v>boltz</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="D2" t="str">
+        <v>FREE AGENCY</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="str">
+        <v>✅ FA SIGNING</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,13 +434,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1784854079769</v>
+        <v>1787471977697</v>
       </c>
       <c r="B2" t="str">
-        <v>Entropiq</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="C2" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -463,13 +463,13 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>1784854026526</v>
+        <v>1787471970177</v>
       </c>
       <c r="B3" t="str">
-        <v>AMKAL</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="C3" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -492,13 +492,13 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1784848026994</v>
+        <v>1787471959675</v>
       </c>
       <c r="B4" t="str">
-        <v>FURIA</v>
+        <v>Fnatic</v>
       </c>
       <c r="C4" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -521,28 +521,28 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1783531248336</v>
+        <v>1784854079769</v>
       </c>
       <c r="B5" t="str">
-        <v>Falcons</v>
+        <v>Entropiq</v>
       </c>
       <c r="C5" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F5" t="str">
         <v>Third</v>
       </c>
       <c r="G5">
-        <v>1790000</v>
+        <v>1500</v>
       </c>
       <c r="H5">
-        <v>100000</v>
+        <v>900</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -550,28 +550,28 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>1783531237020</v>
+        <v>1784854026526</v>
       </c>
       <c r="B6" t="str">
-        <v>Vitality</v>
+        <v>AMKAL</v>
       </c>
       <c r="C6" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F6" t="str">
         <v>Second</v>
       </c>
       <c r="G6">
-        <v>1790000</v>
+        <v>2000</v>
       </c>
       <c r="H6">
-        <v>170000</v>
+        <v>1200</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -579,43 +579,130 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1783531219494</v>
+        <v>1784848026994</v>
       </c>
       <c r="B7" t="str">
-        <v>Iluminar</v>
+        <v>FURIA</v>
       </c>
       <c r="C7" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E7" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F7" t="str">
         <v>Winner</v>
       </c>
       <c r="G7">
+        <v>3000</v>
+      </c>
+      <c r="H7">
+        <v>1800</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>1783531248336</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="C8" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Third</v>
+      </c>
+      <c r="G8">
         <v>1790000</v>
       </c>
-      <c r="H7">
+      <c r="H8">
+        <v>100000</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1783531237020</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="C9" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Second</v>
+      </c>
+      <c r="G9">
+        <v>1790000</v>
+      </c>
+      <c r="H9">
+        <v>170000</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>1783531219494</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="C10" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="G10">
+        <v>1790000</v>
+      </c>
+      <c r="H10">
         <v>500000</v>
       </c>
-      <c r="I7">
+      <c r="I10">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -650,23 +737,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1784854079769-Benkai</v>
-      </c>
-      <c r="B2">
-        <v>1784854079769</v>
+      <c r="A2">
+        <v>1787472254648</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>Benkai</v>
+        <v>REZ</v>
       </c>
       <c r="D2" t="str">
-        <v>Entropiq</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E2" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F2" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -675,30 +762,30 @@
         <v>Regional</v>
       </c>
       <c r="I2" t="str">
-        <v>Third</v>
+        <v>Winner</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>1784854079769-dea</v>
-      </c>
-      <c r="B3">
-        <v>1784854079769</v>
+      <c r="A3">
+        <v>1787472247600</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>dea</v>
+        <v>kr1vda</v>
       </c>
       <c r="D3" t="str">
-        <v>Entropiq</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E3" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F3" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -707,30 +794,30 @@
         <v>Regional</v>
       </c>
       <c r="I3" t="str">
-        <v>Third</v>
+        <v>Winner</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>1784854079769-shane</v>
-      </c>
-      <c r="B4">
-        <v>1784854079769</v>
+      <c r="A4">
+        <v>1787472243903</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
       </c>
       <c r="C4" t="str">
-        <v>shane</v>
+        <v>fear</v>
       </c>
       <c r="D4" t="str">
-        <v>Entropiq</v>
+        <v>Fnatic</v>
       </c>
       <c r="E4" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F4" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -739,30 +826,30 @@
         <v>Regional</v>
       </c>
       <c r="I4" t="str">
-        <v>Third</v>
+        <v>Winner</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>1784854079769-nosraC</v>
-      </c>
-      <c r="B5">
-        <v>1784854079769</v>
+      <c r="A5">
+        <v>1787472232104</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>nosraC</v>
+        <v>KRIMZ</v>
       </c>
       <c r="D5" t="str">
-        <v>Entropiq</v>
+        <v>Fnatic</v>
       </c>
       <c r="E5" t="str">
-        <v>EVENT</v>
+        <v>EVP</v>
       </c>
       <c r="F5" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -771,30 +858,30 @@
         <v>Regional</v>
       </c>
       <c r="I5" t="str">
-        <v>Third</v>
+        <v>Winner</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>1784854079769-MarKE</v>
-      </c>
-      <c r="B6">
-        <v>1784854079769</v>
+      <c r="A6">
+        <v>1787472226864</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>MarKE</v>
+        <v>blameF</v>
       </c>
       <c r="D6" t="str">
-        <v>Entropiq</v>
+        <v>Fnatic</v>
       </c>
       <c r="E6" t="str">
-        <v>EVENT</v>
+        <v>MVP</v>
       </c>
       <c r="F6" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -803,7 +890,7 @@
         <v>Regional</v>
       </c>
       <c r="I6" t="str">
-        <v>Third</v>
+        <v>Winner</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -811,22 +898,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1784854026526-ivz</v>
+        <v>1787471977697-oskar</v>
       </c>
       <c r="B7">
-        <v>1784854026526</v>
+        <v>1787471977697</v>
       </c>
       <c r="C7" t="str">
-        <v>ivz</v>
+        <v>oskar</v>
       </c>
       <c r="D7" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E7" t="str">
         <v>EVENT</v>
       </c>
       <c r="F7" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -835,7 +922,7 @@
         <v>Regional</v>
       </c>
       <c r="I7" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -843,22 +930,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1784854026526-abizz</v>
+        <v>1787471977697-PR</v>
       </c>
       <c r="B8">
-        <v>1784854026526</v>
+        <v>1787471977697</v>
       </c>
       <c r="C8" t="str">
-        <v>abizz</v>
+        <v>PR</v>
       </c>
       <c r="D8" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E8" t="str">
         <v>EVENT</v>
       </c>
       <c r="F8" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -867,7 +954,7 @@
         <v>Regional</v>
       </c>
       <c r="I8" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -875,22 +962,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1784854026526-nacho</v>
+        <v>1787471977697-Tauson</v>
       </c>
       <c r="B9">
-        <v>1784854026526</v>
+        <v>1787471977697</v>
       </c>
       <c r="C9" t="str">
-        <v>nacho</v>
+        <v>Tauson</v>
       </c>
       <c r="D9" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E9" t="str">
         <v>EVENT</v>
       </c>
       <c r="F9" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -899,7 +986,7 @@
         <v>Regional</v>
       </c>
       <c r="I9" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -907,22 +994,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1784854026526-BK1</v>
+        <v>1787471977697-ztr</v>
       </c>
       <c r="B10">
-        <v>1784854026526</v>
+        <v>1787471977697</v>
       </c>
       <c r="C10" t="str">
-        <v>BK1</v>
+        <v>ztr</v>
       </c>
       <c r="D10" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E10" t="str">
         <v>EVENT</v>
       </c>
       <c r="F10" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -931,7 +1018,7 @@
         <v>Regional</v>
       </c>
       <c r="I10" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -939,22 +1026,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1784854026526-next</v>
+        <v>1787471977697-REZ</v>
       </c>
       <c r="B11">
-        <v>1784854026526</v>
+        <v>1787471977697</v>
       </c>
       <c r="C11" t="str">
-        <v>next</v>
+        <v>REZ</v>
       </c>
       <c r="D11" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E11" t="str">
         <v>EVENT</v>
       </c>
       <c r="F11" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -963,7 +1050,7 @@
         <v>Regional</v>
       </c>
       <c r="I11" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -971,22 +1058,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1784848026994-molodoy</v>
+        <v>1787471970177-OneUn1que</v>
       </c>
       <c r="B12">
-        <v>1784848026994</v>
+        <v>1787471970177</v>
       </c>
       <c r="C12" t="str">
-        <v>molodoy</v>
+        <v>OneUn1que</v>
       </c>
       <c r="D12" t="str">
-        <v>FURIA</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E12" t="str">
         <v>EVENT</v>
       </c>
       <c r="F12" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -995,7 +1082,7 @@
         <v>Regional</v>
       </c>
       <c r="I12" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1003,22 +1090,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1784848026994-KSCERATO</v>
+        <v>1787471970177-kL1o</v>
       </c>
       <c r="B13">
-        <v>1784848026994</v>
+        <v>1787471970177</v>
       </c>
       <c r="C13" t="str">
-        <v>KSCERATO</v>
+        <v>kL1o</v>
       </c>
       <c r="D13" t="str">
-        <v>FURIA</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E13" t="str">
         <v>EVENT</v>
       </c>
       <c r="F13" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1027,7 +1114,7 @@
         <v>Regional</v>
       </c>
       <c r="I13" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1035,22 +1122,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>1784848026994-YEKINDAR</v>
+        <v>1787471970177-marat2k</v>
       </c>
       <c r="B14">
-        <v>1784848026994</v>
+        <v>1787471970177</v>
       </c>
       <c r="C14" t="str">
-        <v>YEKINDAR</v>
+        <v>marat2k</v>
       </c>
       <c r="D14" t="str">
-        <v>FURIA</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E14" t="str">
         <v>EVENT</v>
       </c>
       <c r="F14" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1059,7 +1146,7 @@
         <v>Regional</v>
       </c>
       <c r="I14" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1067,22 +1154,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>1784848026994-yuurih</v>
+        <v>1787471970177-Malkiss</v>
       </c>
       <c r="B15">
-        <v>1784848026994</v>
+        <v>1787471970177</v>
       </c>
       <c r="C15" t="str">
-        <v>yuurih</v>
+        <v>Malkiss</v>
       </c>
       <c r="D15" t="str">
-        <v>FURIA</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E15" t="str">
         <v>EVENT</v>
       </c>
       <c r="F15" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1091,7 +1178,7 @@
         <v>Regional</v>
       </c>
       <c r="I15" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1099,22 +1186,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1784848026994-FalleN</v>
+        <v>1787471970177-kr1vda</v>
       </c>
       <c r="B16">
-        <v>1784848026994</v>
+        <v>1787471970177</v>
       </c>
       <c r="C16" t="str">
-        <v>FalleN</v>
+        <v>kr1vda</v>
       </c>
       <c r="D16" t="str">
-        <v>FURIA</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E16" t="str">
         <v>EVENT</v>
       </c>
       <c r="F16" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1123,62 +1210,62 @@
         <v>Regional</v>
       </c>
       <c r="I16" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1787471959675-jambo</v>
+      </c>
+      <c r="B17">
+        <v>1787471959675</v>
+      </c>
+      <c r="C17" t="str">
+        <v>jambo</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Fnatic</v>
+      </c>
+      <c r="E17" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I17" t="str">
         <v>Winner</v>
       </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>1784847962039</v>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v>abizz</v>
-      </c>
-      <c r="D17" t="str">
-        <v>AMKAL</v>
-      </c>
-      <c r="E17" t="str">
-        <v>VP</v>
-      </c>
-      <c r="F17" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Regional</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Second</v>
-      </c>
       <c r="J17">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>1784847955956</v>
-      </c>
-      <c r="B18" t="str">
-        <v/>
+      <c r="A18" t="str">
+        <v>1787471959675-MATYS</v>
+      </c>
+      <c r="B18">
+        <v>1787471959675</v>
       </c>
       <c r="C18" t="str">
-        <v>next</v>
+        <v>MATYS</v>
       </c>
       <c r="D18" t="str">
-        <v>AMKAL</v>
+        <v>Fnatic</v>
       </c>
       <c r="E18" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F18" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1187,30 +1274,30 @@
         <v>Regional</v>
       </c>
       <c r="I18" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>1784847948890</v>
-      </c>
-      <c r="B19" t="str">
-        <v/>
+      <c r="A19" t="str">
+        <v>1787471959675-fear</v>
+      </c>
+      <c r="B19">
+        <v>1787471959675</v>
       </c>
       <c r="C19" t="str">
-        <v>yuurih</v>
+        <v>fear</v>
       </c>
       <c r="D19" t="str">
-        <v>FURIA</v>
+        <v>Fnatic</v>
       </c>
       <c r="E19" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F19" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1226,23 +1313,23 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>1784847943609</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
+      <c r="A20" t="str">
+        <v>1787471959675-blameF</v>
+      </c>
+      <c r="B20">
+        <v>1787471959675</v>
       </c>
       <c r="C20" t="str">
-        <v>KSCERATO</v>
+        <v>blameF</v>
       </c>
       <c r="D20" t="str">
-        <v>FURIA</v>
+        <v>Fnatic</v>
       </c>
       <c r="E20" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F20" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1258,23 +1345,23 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>1784847935905</v>
-      </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="A21" t="str">
+        <v>1787471959675-KRIMZ</v>
+      </c>
+      <c r="B21">
+        <v>1787471959675</v>
       </c>
       <c r="C21" t="str">
-        <v>molodoy</v>
+        <v>KRIMZ</v>
       </c>
       <c r="D21" t="str">
-        <v>FURIA</v>
+        <v>Fnatic</v>
       </c>
       <c r="E21" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F21" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1290,29 +1377,29 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>1783531290361</v>
-      </c>
-      <c r="B22" t="str">
-        <v/>
+      <c r="A22" t="str">
+        <v>1784854079769-Benkai</v>
+      </c>
+      <c r="B22">
+        <v>1784854079769</v>
       </c>
       <c r="C22" t="str">
-        <v>m0NESY</v>
+        <v>Benkai</v>
       </c>
       <c r="D22" t="str">
-        <v>Falcons</v>
+        <v>Entropiq</v>
       </c>
       <c r="E22" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F22" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I22" t="str">
         <v>Third</v>
@@ -1322,128 +1409,128 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>1783531284605</v>
-      </c>
-      <c r="B23" t="str">
-        <v/>
+      <c r="A23" t="str">
+        <v>1784854079769-dea</v>
+      </c>
+      <c r="B23">
+        <v>1784854079769</v>
       </c>
       <c r="C23" t="str">
-        <v>ropz</v>
+        <v>dea</v>
       </c>
       <c r="D23" t="str">
-        <v>Vitality</v>
+        <v>Entropiq</v>
       </c>
       <c r="E23" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F23" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H23" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I23" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>1783531278450</v>
-      </c>
-      <c r="B24" t="str">
-        <v/>
+      <c r="A24" t="str">
+        <v>1784854079769-shane</v>
+      </c>
+      <c r="B24">
+        <v>1784854079769</v>
       </c>
       <c r="C24" t="str">
-        <v>ZywOo</v>
+        <v>shane</v>
       </c>
       <c r="D24" t="str">
-        <v>Vitality</v>
+        <v>Entropiq</v>
       </c>
       <c r="E24" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F24" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H24" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I24" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>1783531271104</v>
-      </c>
-      <c r="B25" t="str">
-        <v/>
+      <c r="A25" t="str">
+        <v>1784854079769-nosraC</v>
+      </c>
+      <c r="B25">
+        <v>1784854079769</v>
       </c>
       <c r="C25" t="str">
-        <v>heroghoxxt</v>
+        <v>nosraC</v>
       </c>
       <c r="D25" t="str">
-        <v>Iluminar</v>
+        <v>Entropiq</v>
       </c>
       <c r="E25" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F25" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H25" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I25" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>1783531262507</v>
-      </c>
-      <c r="B26" t="str">
-        <v/>
+      <c r="A26" t="str">
+        <v>1784854079769-MarKE</v>
+      </c>
+      <c r="B26">
+        <v>1784854079769</v>
       </c>
       <c r="C26" t="str">
-        <v>kilzys</v>
+        <v>MarKE</v>
       </c>
       <c r="D26" t="str">
-        <v>Iluminar</v>
+        <v>Entropiq</v>
       </c>
       <c r="E26" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F26" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H26" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I26" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1451,31 +1538,31 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>1783531248336-kyousuke</v>
+        <v>1784854026526-ivz</v>
       </c>
       <c r="B27">
-        <v>1783531248336</v>
+        <v>1784854026526</v>
       </c>
       <c r="C27" t="str">
-        <v>kyousuke</v>
+        <v>ivz</v>
       </c>
       <c r="D27" t="str">
-        <v>Falcons</v>
+        <v>AMKAL</v>
       </c>
       <c r="E27" t="str">
         <v>EVENT</v>
       </c>
       <c r="F27" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H27" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I27" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1483,31 +1570,31 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>1783531248336-kyxsan</v>
+        <v>1784854026526-abizz</v>
       </c>
       <c r="B28">
-        <v>1783531248336</v>
+        <v>1784854026526</v>
       </c>
       <c r="C28" t="str">
-        <v>kyxsan</v>
+        <v>abizz</v>
       </c>
       <c r="D28" t="str">
-        <v>Falcons</v>
+        <v>AMKAL</v>
       </c>
       <c r="E28" t="str">
         <v>EVENT</v>
       </c>
       <c r="F28" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H28" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I28" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1515,31 +1602,31 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>1783531248336-NiKo</v>
+        <v>1784854026526-nacho</v>
       </c>
       <c r="B29">
-        <v>1783531248336</v>
+        <v>1784854026526</v>
       </c>
       <c r="C29" t="str">
-        <v>NiKo</v>
+        <v>nacho</v>
       </c>
       <c r="D29" t="str">
-        <v>Falcons</v>
+        <v>AMKAL</v>
       </c>
       <c r="E29" t="str">
         <v>EVENT</v>
       </c>
       <c r="F29" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H29" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I29" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1547,31 +1634,31 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>1783531248336-TeSeS</v>
+        <v>1784854026526-BK1</v>
       </c>
       <c r="B30">
-        <v>1783531248336</v>
+        <v>1784854026526</v>
       </c>
       <c r="C30" t="str">
-        <v>TeSeS</v>
+        <v>BK1</v>
       </c>
       <c r="D30" t="str">
-        <v>Falcons</v>
+        <v>AMKAL</v>
       </c>
       <c r="E30" t="str">
         <v>EVENT</v>
       </c>
       <c r="F30" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H30" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I30" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1579,31 +1666,31 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>1783531248336-m0NESY</v>
+        <v>1784854026526-next</v>
       </c>
       <c r="B31">
-        <v>1783531248336</v>
+        <v>1784854026526</v>
       </c>
       <c r="C31" t="str">
-        <v>m0NESY</v>
+        <v>next</v>
       </c>
       <c r="D31" t="str">
-        <v>Falcons</v>
+        <v>AMKAL</v>
       </c>
       <c r="E31" t="str">
         <v>EVENT</v>
       </c>
       <c r="F31" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H31" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I31" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1611,31 +1698,31 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>1783531237020-mezii</v>
+        <v>1784848026994-molodoy</v>
       </c>
       <c r="B32">
-        <v>1783531237020</v>
+        <v>1784848026994</v>
       </c>
       <c r="C32" t="str">
-        <v>mezii</v>
+        <v>molodoy</v>
       </c>
       <c r="D32" t="str">
-        <v>Vitality</v>
+        <v>FURIA</v>
       </c>
       <c r="E32" t="str">
         <v>EVENT</v>
       </c>
       <c r="F32" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H32" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I32" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1643,31 +1730,31 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>1783531237020-flameZ</v>
+        <v>1784848026994-KSCERATO</v>
       </c>
       <c r="B33">
-        <v>1783531237020</v>
+        <v>1784848026994</v>
       </c>
       <c r="C33" t="str">
-        <v>flameZ</v>
+        <v>KSCERATO</v>
       </c>
       <c r="D33" t="str">
-        <v>Vitality</v>
+        <v>FURIA</v>
       </c>
       <c r="E33" t="str">
         <v>EVENT</v>
       </c>
       <c r="F33" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H33" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I33" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1675,31 +1762,31 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>1783531237020-ropz</v>
+        <v>1784848026994-YEKINDAR</v>
       </c>
       <c r="B34">
-        <v>1783531237020</v>
+        <v>1784848026994</v>
       </c>
       <c r="C34" t="str">
-        <v>ropz</v>
+        <v>YEKINDAR</v>
       </c>
       <c r="D34" t="str">
-        <v>Vitality</v>
+        <v>FURIA</v>
       </c>
       <c r="E34" t="str">
         <v>EVENT</v>
       </c>
       <c r="F34" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H34" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I34" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1707,31 +1794,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>1783531237020-apEX</v>
+        <v>1784848026994-yuurih</v>
       </c>
       <c r="B35">
-        <v>1783531237020</v>
+        <v>1784848026994</v>
       </c>
       <c r="C35" t="str">
-        <v>apEX</v>
+        <v>yuurih</v>
       </c>
       <c r="D35" t="str">
-        <v>Vitality</v>
+        <v>FURIA</v>
       </c>
       <c r="E35" t="str">
         <v>EVENT</v>
       </c>
       <c r="F35" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H35" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I35" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -1739,124 +1826,124 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>1783531237020-ZywOo</v>
+        <v>1784848026994-FalleN</v>
       </c>
       <c r="B36">
-        <v>1783531237020</v>
+        <v>1784848026994</v>
       </c>
       <c r="C36" t="str">
-        <v>ZywOo</v>
+        <v>FalleN</v>
       </c>
       <c r="D36" t="str">
-        <v>Vitality</v>
+        <v>FURIA</v>
       </c>
       <c r="E36" t="str">
         <v>EVENT</v>
       </c>
       <c r="F36" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H36" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I36" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1784847962039</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>abizz</v>
+      </c>
+      <c r="D37" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E37" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F37" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I37" t="str">
         <v>Second</v>
       </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>1783531219494-history</v>
-      </c>
-      <c r="B37">
-        <v>1783531219494</v>
-      </c>
-      <c r="C37" t="str">
-        <v>history</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="E37" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="F37" t="str">
-        <v>DreamHack Winter 2026</v>
-      </c>
-      <c r="G37">
-        <v>5</v>
-      </c>
-      <c r="H37" t="str">
-        <v>Global</v>
-      </c>
-      <c r="I37" t="str">
-        <v>Winner</v>
-      </c>
       <c r="J37">
         <v>1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>1783531219494-heroghoxxt</v>
-      </c>
-      <c r="B38">
-        <v>1783531219494</v>
+      <c r="A38">
+        <v>1784847955956</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
       </c>
       <c r="C38" t="str">
-        <v>heroghoxxt</v>
+        <v>next</v>
       </c>
       <c r="D38" t="str">
-        <v>Iluminar</v>
+        <v>AMKAL</v>
       </c>
       <c r="E38" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F38" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H38" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I38" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>1783531219494-SpavaQu</v>
-      </c>
-      <c r="B39">
-        <v>1783531219494</v>
+      <c r="A39">
+        <v>1784847948890</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
       </c>
       <c r="C39" t="str">
-        <v>SpavaQu</v>
+        <v>yuurih</v>
       </c>
       <c r="D39" t="str">
-        <v>Iluminar</v>
+        <v>FURIA</v>
       </c>
       <c r="E39" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F39" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H39" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I39" t="str">
         <v>Winner</v>
@@ -1866,29 +1953,29 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>1783531219494-Pelle</v>
-      </c>
-      <c r="B40">
-        <v>1783531219494</v>
+      <c r="A40">
+        <v>1784847943609</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
       </c>
       <c r="C40" t="str">
-        <v>Pelle</v>
+        <v>KSCERATO</v>
       </c>
       <c r="D40" t="str">
-        <v>Iluminar</v>
+        <v>FURIA</v>
       </c>
       <c r="E40" t="str">
-        <v>EVENT</v>
+        <v>EVP</v>
       </c>
       <c r="F40" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H40" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I40" t="str">
         <v>Winner</v>
@@ -1898,29 +1985,29 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>1783531219494-kilzys</v>
-      </c>
-      <c r="B41">
-        <v>1783531219494</v>
+      <c r="A41">
+        <v>1784847935905</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
       </c>
       <c r="C41" t="str">
-        <v>kilzys</v>
+        <v>molodoy</v>
       </c>
       <c r="D41" t="str">
-        <v>Iluminar</v>
+        <v>FURIA</v>
       </c>
       <c r="E41" t="str">
-        <v>EVENT</v>
+        <v>MVP</v>
       </c>
       <c r="F41" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H41" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I41" t="str">
         <v>Winner</v>
@@ -1929,9 +2016,649 @@
         <v>1</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42">
+        <v>1783531290361</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E42" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F42" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G42">
+        <v>5</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Third</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1783531284605</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E43" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F43" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>1783531278450</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E44" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F44" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G44">
+        <v>5</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>1783531271104</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E45" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F45" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>1783531262507</v>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E46" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F46" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G46">
+        <v>5</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>1783531248336-kyousuke</v>
+      </c>
+      <c r="B47">
+        <v>1783531248336</v>
+      </c>
+      <c r="C47" t="str">
+        <v>kyousuke</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E47" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F47" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G47">
+        <v>5</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Third</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>1783531248336-kyxsan</v>
+      </c>
+      <c r="B48">
+        <v>1783531248336</v>
+      </c>
+      <c r="C48" t="str">
+        <v>kyxsan</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E48" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F48" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Third</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>1783531248336-NiKo</v>
+      </c>
+      <c r="B49">
+        <v>1783531248336</v>
+      </c>
+      <c r="C49" t="str">
+        <v>NiKo</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E49" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F49" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G49">
+        <v>5</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Third</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>1783531248336-TeSeS</v>
+      </c>
+      <c r="B50">
+        <v>1783531248336</v>
+      </c>
+      <c r="C50" t="str">
+        <v>TeSeS</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E50" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F50" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G50">
+        <v>5</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Third</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>1783531248336-m0NESY</v>
+      </c>
+      <c r="B51">
+        <v>1783531248336</v>
+      </c>
+      <c r="C51" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E51" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F51" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G51">
+        <v>5</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Third</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>1783531237020-mezii</v>
+      </c>
+      <c r="B52">
+        <v>1783531237020</v>
+      </c>
+      <c r="C52" t="str">
+        <v>mezii</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E52" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F52" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G52">
+        <v>5</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>1783531237020-flameZ</v>
+      </c>
+      <c r="B53">
+        <v>1783531237020</v>
+      </c>
+      <c r="C53" t="str">
+        <v>flameZ</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E53" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F53" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G53">
+        <v>5</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>1783531237020-ropz</v>
+      </c>
+      <c r="B54">
+        <v>1783531237020</v>
+      </c>
+      <c r="C54" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E54" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F54" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G54">
+        <v>5</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>1783531237020-apEX</v>
+      </c>
+      <c r="B55">
+        <v>1783531237020</v>
+      </c>
+      <c r="C55" t="str">
+        <v>apEX</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E55" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F55" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G55">
+        <v>5</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>1783531237020-ZywOo</v>
+      </c>
+      <c r="B56">
+        <v>1783531237020</v>
+      </c>
+      <c r="C56" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E56" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F56" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G56">
+        <v>5</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Second</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>1783531219494-history</v>
+      </c>
+      <c r="B57">
+        <v>1783531219494</v>
+      </c>
+      <c r="C57" t="str">
+        <v>history</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E57" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F57" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G57">
+        <v>5</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>1783531219494-heroghoxxt</v>
+      </c>
+      <c r="B58">
+        <v>1783531219494</v>
+      </c>
+      <c r="C58" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E58" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F58" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G58">
+        <v>5</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>1783531219494-SpavaQu</v>
+      </c>
+      <c r="B59">
+        <v>1783531219494</v>
+      </c>
+      <c r="C59" t="str">
+        <v>SpavaQu</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E59" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F59" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G59">
+        <v>5</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>1783531219494-Pelle</v>
+      </c>
+      <c r="B60">
+        <v>1783531219494</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Pelle</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E60" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F60" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G60">
+        <v>5</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>1783531219494-kilzys</v>
+      </c>
+      <c r="B61">
+        <v>1783531219494</v>
+      </c>
+      <c r="C61" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E61" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F61" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G61">
+        <v>5</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -2665,7 +2665,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2695,42 +2695,42 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1785396043745</v>
+        <v>1787536348426</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>PROMOTED</v>
+        <v>RELEASED</v>
       </c>
       <c r="D2" t="str">
-        <v>boltz</v>
+        <v>fer</v>
       </c>
       <c r="E2" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="F2" t="str">
-        <v>Lux Tenebris</v>
+        <v>Free Agency</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="str">
-        <v>promoted to starter</v>
+        <v>released to market for free</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1785396042996</v>
+        <v>1785396043745</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>BENCHED</v>
+        <v>PROMOTED</v>
       </c>
       <c r="D3" t="str">
-        <v>fer</v>
+        <v>boltz</v>
       </c>
       <c r="E3" t="str">
         <v>Lux Tenebris</v>
@@ -2742,24 +2742,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="str">
-        <v>moved to bench</v>
+        <v>promoted to starter</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1785396011356</v>
+        <v>1785396042996</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="str">
-        <v>FA SIGNING</v>
+        <v>BENCHED</v>
       </c>
       <c r="D4" t="str">
-        <v>boltz</v>
+        <v>fer</v>
       </c>
       <c r="E4" t="str">
-        <v>Free Agency</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="F4" t="str">
         <v>Lux Tenebris</v>
@@ -2768,12 +2768,12 @@
         <v>0</v>
       </c>
       <c r="H4" t="str">
-        <v>joined as Bench</v>
+        <v>moved to bench</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>1783532394458</v>
+        <v>1785396011356</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -2782,128 +2782,128 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D5" t="str">
-        <v>diskyb0b</v>
+        <v>boltz</v>
       </c>
       <c r="E5" t="str">
         <v>Free Agency</v>
       </c>
       <c r="F5" t="str">
-        <v>Kappa Bar</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="str">
-        <v>joined as Starter</v>
+        <v>joined as Bench</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1783532378345</v>
+        <v>1783532394458</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D6" t="str">
-        <v>Gizmy</v>
+        <v>diskyb0b</v>
       </c>
       <c r="E6" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F6" t="str">
         <v>Kappa Bar</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Iluminar</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Starter</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>1783532335269</v>
+        <v>1783532378345</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D7" t="str">
-        <v>hades</v>
+        <v>Gizmy</v>
       </c>
       <c r="E7" t="str">
-        <v>Free Agency</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="F7" t="str">
-        <v>Mythic</v>
+        <v>Iluminar</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="str">
-        <v>joined as Starter</v>
+        <v>CLAUSE DEAL · joined as Starter</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>1783532286477</v>
+        <v>1783532335269</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D8" t="str">
-        <v>fl0m</v>
+        <v>hades</v>
       </c>
       <c r="E8" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F8" t="str">
         <v>Mythic</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Iluminar</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Starter</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>1783531772696</v>
+        <v>1783532286477</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D9" t="str">
-        <v>taco</v>
+        <v>fl0m</v>
       </c>
       <c r="E9" t="str">
-        <v>Free Agency</v>
+        <v>Mythic</v>
       </c>
       <c r="F9" t="str">
-        <v>Lux Tenebris</v>
+        <v>Iluminar</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="str">
-        <v>joined as Starter</v>
+        <v>CLAUSE DEAL · joined as Starter</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>1783531758984</v>
+        <v>1783531772696</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2912,7 +2912,7 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D10" t="str">
-        <v>fer</v>
+        <v>taco</v>
       </c>
       <c r="E10" t="str">
         <v>Free Agency</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>1783531616692</v>
+        <v>1783531758984</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2938,7 +2938,7 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D11" t="str">
-        <v>kyourezz</v>
+        <v>fer</v>
       </c>
       <c r="E11" t="str">
         <v>Free Agency</v>
@@ -2955,33 +2955,33 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>1783531586211</v>
+        <v>1783531616692</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D12" t="str">
-        <v>heroghoxxt</v>
+        <v>kyourezz</v>
       </c>
       <c r="E12" t="str">
-        <v>Iluminar</v>
+        <v>Free Agency</v>
       </c>
       <c r="F12" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="G12">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="H12" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Starter</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>1783531583393</v>
+        <v>1783531586211</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2990,7 +2990,7 @@
         <v>TRANSFER</v>
       </c>
       <c r="D13" t="str">
-        <v>kilzys</v>
+        <v>heroghoxxt</v>
       </c>
       <c r="E13" t="str">
         <v>Iluminar</v>
@@ -2999,7 +2999,7 @@
         <v>Lux Tenebris</v>
       </c>
       <c r="G13">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="H13" t="str">
         <v>CLAUSE DEAL · joined as Starter</v>
@@ -3007,33 +3007,33 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>1783473413103</v>
+        <v>1783531583393</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D14" t="str">
-        <v>taco</v>
+        <v>kilzys</v>
       </c>
       <c r="E14" t="str">
-        <v>Free Agency</v>
+        <v>Iluminar</v>
       </c>
       <c r="F14" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H14" t="str">
-        <v>joined as Starter</v>
+        <v>CLAUSE DEAL · joined as Starter</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>1783473388452</v>
+        <v>1783473413103</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -3042,7 +3042,7 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D15" t="str">
-        <v>fer</v>
+        <v>taco</v>
       </c>
       <c r="E15" t="str">
         <v>Free Agency</v>
@@ -3057,16 +3057,42 @@
         <v>joined as Starter</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16">
+        <v>1783473388452</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D16" t="str">
+        <v>fer</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="str">
+        <v>joined as Starter</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3093,30 +3119,53 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1785396010605</v>
+        <v>1787536347803</v>
       </c>
       <c r="B2" t="str">
-        <v>boltz</v>
+        <v>fer</v>
       </c>
       <c r="C2" t="str">
+        <v>—</v>
+      </c>
+      <c r="D2" t="str">
         <v>Lux Tenebris</v>
-      </c>
-      <c r="D2" t="str">
-        <v>FREE AGENCY</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="str">
+        <v>✅ RELEASED (FREE)</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1785396010605</v>
+      </c>
+      <c r="B3" t="str">
+        <v>boltz</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="D3" t="str">
+        <v>FREE AGENCY</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="str">
         <v>✅ FA SIGNING</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>
